--- a/8.sınıf öğrencileri.xlsx
+++ b/8.sınıf öğrencileri.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24686" windowHeight="11606"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24686" windowHeight="11606" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sayfa2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="130">
   <si>
     <t>DERİN VARLI</t>
   </si>
@@ -363,14 +364,59 @@
     <t>ad_soyad</t>
   </si>
   <si>
-    <t>NESLİHAN DEMİREL</t>
+    <t>HATİCE ALPAY</t>
+  </si>
+  <si>
+    <t>FERHAT ATMACA</t>
+  </si>
+  <si>
+    <t>ALP BARTU ALTINKAYA</t>
+  </si>
+  <si>
+    <t>NİL KARACA CANBAY</t>
+  </si>
+  <si>
+    <t>EYLÜL YILDIRIM</t>
+  </si>
+  <si>
+    <t>NİSA YARGIÇ</t>
+  </si>
+  <si>
+    <t>HAVEL BENZAN TEKDEMİR</t>
+  </si>
+  <si>
+    <t>BELİNAY TAŞKIRAN</t>
+  </si>
+  <si>
+    <t>MUSTAFA EMİR SAVAN</t>
+  </si>
+  <si>
+    <t>ÖYKÜ ELİF ÖZTURAN</t>
+  </si>
+  <si>
+    <t>AZRA ZEYNEP IŞIK</t>
+  </si>
+  <si>
+    <t>AHMET EREN KIRCALI</t>
+  </si>
+  <si>
+    <t>BEYZA GÜL KARABULUT</t>
+  </si>
+  <si>
+    <t>MUHAMMED MİRAÇ  ENGİN</t>
+  </si>
+  <si>
+    <t>SERHAT ATMACA</t>
+  </si>
+  <si>
+    <t>MURAT STAHLSCHMİDT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -396,6 +442,14 @@
       <charset val="162"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -405,7 +459,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -428,11 +482,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -441,6 +506,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -723,7 +794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A117"/>
+  <dimension ref="A1:A116"/>
   <sheetFormatPr defaultRowHeight="18.45" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="37.3046875" style="3" customWidth="1"/>
@@ -1026,296 +1097,384 @@
     </row>
     <row r="60" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2" t="s">
-        <v>114</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="64" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="67" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="68" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="69" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="70" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="71" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="72" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="73" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="75" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="76" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="78" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="79" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="86" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="87" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="88" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="89" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="90" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="91" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="2" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
     </row>
     <row r="93" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A94" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A95" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A96" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A97" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A98" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A99" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A100" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A101" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A102" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A103" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A104" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A105" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A106" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A107" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A108" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A109" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A110" s="2" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A111" s="2" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A112" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A113" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A114" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A115" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A116" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A117" s="2" t="s">
         <v>112</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="30.61328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="18.45" x14ac:dyDescent="0.4">
+      <c r="A1" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="18.45" x14ac:dyDescent="0.4">
+      <c r="A2" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="18.45" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="18.45" x14ac:dyDescent="0.4">
+      <c r="A4" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="18.45" x14ac:dyDescent="0.4">
+      <c r="A5" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="18.45" x14ac:dyDescent="0.4">
+      <c r="A6" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="18.45" x14ac:dyDescent="0.4">
+      <c r="A7" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="18.45" x14ac:dyDescent="0.4">
+      <c r="A8" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="18.45" x14ac:dyDescent="0.4">
+      <c r="A9" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="18.45" x14ac:dyDescent="0.4">
+      <c r="A10" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="18.45" x14ac:dyDescent="0.4">
+      <c r="A11" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="18.45" x14ac:dyDescent="0.4">
+      <c r="A12" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="18.45" x14ac:dyDescent="0.4">
+      <c r="A13" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="18.45" x14ac:dyDescent="0.4">
+      <c r="A14" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="18.45" x14ac:dyDescent="0.4">
+      <c r="A15" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="18.45" x14ac:dyDescent="0.4">
+      <c r="A16" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/8.sınıf öğrencileri.xlsx
+++ b/8.sınıf öğrencileri.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24686" windowHeight="11606" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24686" windowHeight="11606"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="182">
   <si>
     <t>DERİN VARLI</t>
   </si>
@@ -410,6 +410,162 @@
   </si>
   <si>
     <t>MURAT STAHLSCHMİDT</t>
+  </si>
+  <si>
+    <t>ENES ÇAĞAN ORHAN</t>
+  </si>
+  <si>
+    <t>METİN MERT BALCI</t>
+  </si>
+  <si>
+    <t>GÜLSU YÜCE</t>
+  </si>
+  <si>
+    <t>EFE ALAKUŞAK</t>
+  </si>
+  <si>
+    <t>ZEYNEP ECE ARSLAN</t>
+  </si>
+  <si>
+    <t>ELİF SAYKAL</t>
+  </si>
+  <si>
+    <t>MEHMETHAN KEÇECİ</t>
+  </si>
+  <si>
+    <t>RIDVAN OZAN SON</t>
+  </si>
+  <si>
+    <t>ASIM DEMİRTAŞ</t>
+  </si>
+  <si>
+    <t>MEHLİKA BETÜL ALTUNTAŞ</t>
+  </si>
+  <si>
+    <t>MİRAÇ KOMAR</t>
+  </si>
+  <si>
+    <t>MUSTAFA İRFAN TORUN</t>
+  </si>
+  <si>
+    <t>CEYHUN DEMİRCİ</t>
+  </si>
+  <si>
+    <t>AYÇA ELA ŞEN</t>
+  </si>
+  <si>
+    <t>ECE İĞDELİOĞLU</t>
+  </si>
+  <si>
+    <t>ZEYNEP ELA ÇALIŞKAN</t>
+  </si>
+  <si>
+    <t>CEMRE BETÜL ÇALIŞKAN</t>
+  </si>
+  <si>
+    <t>BURAK İSMAİL SEYMEN</t>
+  </si>
+  <si>
+    <t>BUĞRA TAHA KAYABAŞI</t>
+  </si>
+  <si>
+    <t>BUĞLEM İKRA KAYABAŞI</t>
+  </si>
+  <si>
+    <t>DERİN TOPÇUOĞLU</t>
+  </si>
+  <si>
+    <t>BUĞLEM NİSA BAŞARAN</t>
+  </si>
+  <si>
+    <t>ELİSA KÖROĞLU</t>
+  </si>
+  <si>
+    <t>ELİF EYLÜL FURUNCI</t>
+  </si>
+  <si>
+    <t>URAS SELÇUK</t>
+  </si>
+  <si>
+    <t>ECMEL YASİR KORKMAZ</t>
+  </si>
+  <si>
+    <t>ATA YUSUF KARSLI</t>
+  </si>
+  <si>
+    <t>EYLÜL BUĞLEM ULUTAŞ</t>
+  </si>
+  <si>
+    <t>ELÇİN KUDU</t>
+  </si>
+  <si>
+    <t>AKIN TURHAN</t>
+  </si>
+  <si>
+    <t>YALIN TURHAN</t>
+  </si>
+  <si>
+    <t>ERKAN POYRAZ TEKİN</t>
+  </si>
+  <si>
+    <t>EMİR ÖZKAN</t>
+  </si>
+  <si>
+    <t>BERAT EMİR ERGÖN</t>
+  </si>
+  <si>
+    <t>KEREM EYMEN BOYDAŞ</t>
+  </si>
+  <si>
+    <t>MUHAMMET ENES YILDIZ</t>
+  </si>
+  <si>
+    <t>MEHMET EREN ÇAĞLAYAN</t>
+  </si>
+  <si>
+    <t>ELİF ESMA GÖK</t>
+  </si>
+  <si>
+    <t>ASEL DURU CANKURTARAN</t>
+  </si>
+  <si>
+    <t>BULUT CEMAL SAKA</t>
+  </si>
+  <si>
+    <t>EFSUN ARABACI</t>
+  </si>
+  <si>
+    <t>ÖYKÜ ÖGECİK</t>
+  </si>
+  <si>
+    <t>MELEK SEDEN BOZBAY</t>
+  </si>
+  <si>
+    <t>MİRAÇ POLAT</t>
+  </si>
+  <si>
+    <t>NİHAN SOLMAZ</t>
+  </si>
+  <si>
+    <t>KÖKSAL KİZİR</t>
+  </si>
+  <si>
+    <t>DEFNE GENÇ</t>
+  </si>
+  <si>
+    <t>RÜYA TATAR</t>
+  </si>
+  <si>
+    <t>İSMAİL CENGİZ ARSLANTÜRK</t>
+  </si>
+  <si>
+    <t>ASYA MİNA CEYLAN</t>
+  </si>
+  <si>
+    <t>ELİF KARATAŞ</t>
+  </si>
+  <si>
+    <t>EFKAN REFİK GÜMÜŞ</t>
   </si>
 </sst>
 </file>
@@ -451,12 +607,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -497,7 +659,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -512,6 +674,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -794,7 +965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A116"/>
+  <dimension ref="A1:A184"/>
   <sheetFormatPr defaultRowHeight="18.45" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="37.3046875" style="3" customWidth="1"/>
@@ -1378,6 +1549,346 @@
     <row r="116" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A116" s="2" t="s">
         <v>112</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A117" s="8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A118" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A119" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A120" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A121" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A122" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A123" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A124" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A125" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A126" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A127" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A128" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A129" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A130" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A131" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A132" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A133" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A134" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A135" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A136" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A137" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A138" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A139" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A140" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A141" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A142" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A143" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A144" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A145" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A146" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A147" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A148" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A149" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A150" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A151" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A152" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A153" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A154" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A155" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A156" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A157" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A158" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A159" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A160" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A161" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A162" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A163" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A164" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A165" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A166" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A167" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A168" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A169" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A170" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A171" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A172" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A173" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A174" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A175" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A176" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A177" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A178" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A179" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A180" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A181" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A182" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A183" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A184" s="3" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
